--- a/reports/meta_intel_2026-W24.xlsx
+++ b/reports/meta_intel_2026-W24.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-08 11:31 UTC</t>
+          <t>Generated: 2026-06-08 16:47 UTC</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -980,36 +980,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1337913301639544</t>
+          <t>1262827105689733</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>mariavpaul with Remento</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>I decided I wasn't going to miss the chance to ask so many more questions... Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. Sorry, we're having trouble playing this video.</t>
+          <t>Living far from grandparents means missing so many everyday moments. That’s why I love Remento @getremento ✨ Instead of letting family stories fade away, my dad can simply talk, and those memories become a keepsake book my kids can treasure forever.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>The next best thing to having Grandpa right there ❤️</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1025,7 +1020,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3911192652519370</t>
+          <t>1337913301639544</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1035,21 +1030,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The most meaningful Father’s Day gift: his voice, forever at your fingertips. Why families love it: 📱 No downloads, logins, or passwords</t>
+          <t>I decided I wasn't going to miss the chance to ask so many more questions... Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1065,31 +1065,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1775246913443819</t>
+          <t>3911192652519370</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>legacyofagrandpa with Remento</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>I don’t say yes to many partnerships, but this one hit me personally. Lately, I’ve been thinking about how many stories quietly disappear over time. Not because they weren’t important… but because nobody ever captured them. The stories about childhood.</t>
+          <t>The most meaningful Father’s Day gift: his voice, forever at your fingertips. Why families love it: 📱 No downloads, logins, or passwords</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lessons learned.</t>
+          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1105,31 +1105,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1509948420588575</t>
+          <t>1775246913443819</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Everyday Chiffon with Remento</t>
+          <t>legacyofagrandpa with Remento</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>THE Father’s Day gift 👏🏽 Comment BOOK &amp; I’ll send you 🔗’s @getremento has got to be the coolest gift out there &amp; something generations to come can enjoy. Bring your dads stories to life &amp; forever get to watch him tell them 🥹 we got emotional looking back!! So sweet. The gift for the man who has everything 💙 #fathersday #fatherdaughter #fathersdaygift #remento #fathersdaygiftideas</t>
+          <t>I don’t say yes to many partnerships, but this one hit me personally. Lately, I’ve been thinking about how many stories quietly disappear over time. Not because they weren’t important… but because nobody ever captured them. The stories about childhood.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Father’s Day gift idea, father daughter</t>
+          <t>Lessons learned.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1880751212615328</t>
+          <t>1509948420588575</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Everyday Chiffon with Remento</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>THE Father’s Day gift 👏🏽 Comment BOOK &amp; I’ll send you 🔗’s @getremento has got to be the coolest gift out there &amp; something generations to come can enjoy. Bring your dads stories to life &amp; forever get to watch him tell them 🥹 we got emotional looking back!! So sweet. The gift for the man who has everything 💙 #fathersday #fatherdaughter #fathersdaygift #remento #fathersdaygiftideas</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Father’s Day gift idea, father daughter</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>970418362567584</t>
+          <t>1880751212615328</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remento with Remento</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1205,11 +1205,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4064887613808452</t>
+          <t>1005033832467461</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1395,21 +1395,21 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>As seen on Shark Tank: the ONLY book dad writes without writing a word, AND it has his voice inside. Why dad's love it: 📱 No downloads, logins, or passwords</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1425,31 +1425,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1005033832467461</t>
+          <t>1748597059631955</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Adadnamedrory with Remento</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>If you’re looking for a meaningful gift for a parent or grandparent, I highly recommend Remento. I was honestly surprised by how much it impacted me when I received the finished book. The quality is incredible—the binding, the glossy photos, the overall feel of it. It doesn’t feel like just another photo book. It feels personal. It feels real. One of the things I love most is that it captures stories, memories, advice, and even voice recordings, creating something future generations can treasure.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1465,26 +1460,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1748597059631955</t>
+          <t>26955183910799087</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Adadnamedrory with Remento</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>If you’re looking for a meaningful gift for a parent or grandparent, I highly recommend Remento. I was honestly surprised by how much it impacted me when I received the finished book. The quality is incredible—the binding, the glossy photos, the overall feel of it. It doesn’t feel like just another photo book. It feels personal. It feels real. One of the things I love most is that it captures stories, memories, advice, and even voice recordings, creating something future generations can treasure.</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>26955183910799087</t>
+          <t>1265645248982771</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1510,21 +1510,21 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>As seen on Shark Tank: the ONLY book dad writes without writing a word, AND it has his voice inside. Why dad's love it: 📱 No downloads, logins, or passwords</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1265645248982771</t>
+          <t>1533345218419188</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>As seen on Shark Tank: the ONLY book dad writes without writing a word, AND it has his voice inside. Why dad's love it: 📱 No downloads, logins, or passwords</t>
+          <t>The most meaningful Father’s Day gift: his voice, forever at your fingertips. Why families love it: 📱 No downloads, logins, or passwords</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1533345218419188</t>
+          <t>2157849958282307</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1590,21 +1590,21 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The most meaningful Father’s Day gift: his voice, forever at your fingertips. Why families love it: 📱 No downloads, logins, or passwords</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2157849958282307</t>
+          <t>26677419218566558</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1640,11 +1640,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1496684578006716</t>
+          <t>1333466355410690</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Learn more</t>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2071219660470847</t>
+          <t>1496684578006716</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3015,26 +3015,26 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>This Book Made My Dad Cry (In a Good Way).</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2165050094062397</t>
+          <t>2071219660470847</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3060,26 +3060,26 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Learn more</t>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4564425283883218</t>
+          <t>2165050094062397</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1631994437866750</t>
+          <t>4564425283883218</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1726022011744222</t>
+          <t>1631994437866750</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>969167216028774</t>
+          <t>1726022011744222</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>974049545525369</t>
+          <t>969167216028774</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>824548033811820</t>
+          <t>974049545525369</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Low impression count Sorry, we're having trouble playing this video.</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>877547294682816</t>
+          <t>824548033811820</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Skip the typing, editing, and overwhelm. Storykeeper records voices naturally and turns them into a handcrafted book. Effortless, modern and filled with the moments that matter most. Low impression count Sorry, we're having trouble playing this video.</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Low impression count Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1305482504525889</t>
+          <t>877547294682816</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3420,12 +3420,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. Low impression count WWW.STORYKEEPER.COM</t>
+          <t>Skip the typing, editing, and overwhelm. Storykeeper records voices naturally and turns them into a handcrafted book. Effortless, modern and filled with the moments that matter most. Low impression count Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>This Book Made My Dad Cry (In a Good Way).</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3450,7 +3455,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>884035753955138</t>
+          <t>1305482504525889</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3460,12 +3465,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. Low impression count WWW.STORYKEEPER.COM</t>
+          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. Low impression count WWW.STORYKEEPER.COM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Record. Print. Keep Forever</t>
+          <t>This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3490,7 +3495,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1314583030805433</t>
+          <t>884035753955138</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3510,11 +3515,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4562234493988358</t>
+          <t>1314583030805433</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3540,21 +3545,21 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Give him a lifetime of memories instead of another throwaway present. Start his StoryKeeper book today. Low impression count Skip the generic Father’s Day gifts</t>
+          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. Low impression count WWW.STORYKEEPER.COM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Give him a lifetime of memories.</t>
+          <t>Record. Print. Keep Forever</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3570,7 +3575,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26907492185598691</t>
+          <t>4562234493988358</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3580,21 +3585,21 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Give more than a gift—give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.UK The Gift They’ll Never Forget.</t>
+          <t>Give him a lifetime of memories instead of another throwaway present. Start his StoryKeeper book today. Low impression count Skip the generic Father’s Day gifts</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Give a gift that becomes a family heirloom—one story at a time.</t>
+          <t>Give him a lifetime of memories.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3610,7 +3615,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1307636784329203</t>
+          <t>26907492185598691</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3620,21 +3625,21 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>It looks like a book, but it speaks from the heart. StoryKeeper turns voices and memories into something you can open, hold, and hear. Low impression count</t>
+          <t>Give more than a gift—give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.UK The Gift They’ll Never Forget.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Give a gift that becomes a family heirloom—one story at a time.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3650,7 +3655,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2265135094294745</t>
+          <t>1307636784329203</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3660,17 +3665,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>StoryKeeper makes it easy to capture memories. No setup, no stress, no tech overwhelm. Just stories, told and transformed beautifully. Low impression count Sorry, we're having trouble playing this video.</t>
+          <t>It looks like a book, but it speaks from the heart. StoryKeeper turns voices and memories into something you can open, hold, and hear. Low impression count</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Learn more</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>973998952205878</t>
+          <t>2265135094294745</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3705,21 +3705,26 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. Low impression count WWW.STORYKEEPER.COM</t>
+          <t>StoryKeeper makes it easy to capture memories. No setup, no stress, no tech overwhelm. Just stories, told and transformed beautifully. Low impression count Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>The Only Book That Let's You Listen to Their Story.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3730,41 +3735,36 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ElliQ</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1685628942752739</t>
+          <t>1888598388471432</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ElliQ</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Low impression count</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3775,41 +3775,36 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ElliQ</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1688004719222897</t>
+          <t>973998952205878</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ElliQ</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. Low impression count WWW.STORYKEEPER.COM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>The Only Book That Let's You Listen to Their Story.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3820,41 +3815,36 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ElliQ</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2082672142583809</t>
+          <t>2438857833193853</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ElliQ</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Low impression count</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3870,7 +3860,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>25522883924055159</t>
+          <t>1685628942752739</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3880,21 +3870,26 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>✨ Daily check-ins &amp; reminders</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3910,7 +3905,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>838679825886616</t>
+          <t>1688004719222897</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3920,21 +3915,26 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>✨ A friendly voice</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1488992326012147</t>
+          <t>2082672142583809</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
+          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3975,11 +3975,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1682907829804633</t>
+          <t>25522883924055159</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4005,26 +4005,21 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>✨ Daily check-ins &amp; reminders</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4040,7 +4035,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>944975184903429</t>
+          <t>838679825886616</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4050,26 +4045,21 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4085,7 +4075,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>993138953210800</t>
+          <t>1488992326012147</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4110,11 +4100,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4130,7 +4120,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1948413482455351</t>
+          <t>1682907829804633</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4140,21 +4130,26 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>It’s helping them continue to thrive there ✨</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4170,7 +4165,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>26794090103575688</t>
+          <t>944975184903429</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4180,21 +4175,26 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>It’s helping them continue to thrive there ✨</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2383639082136267</t>
+          <t>993138953210800</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4220,21 +4220,26 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>✨ A friendly voice</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4250,7 +4255,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1773179040333547</t>
+          <t>1948413482455351</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4260,21 +4265,21 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>✨ A friendly voice</t>
+          <t>It’s helping them continue to thrive there ✨</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3778152075652558</t>
+          <t>26794090103575688</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4300,21 +4305,21 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>✨ A friendly voice</t>
+          <t>It’s helping them continue to thrive there ✨</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4330,7 +4335,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1456990959516034</t>
+          <t>2383639082136267</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4340,26 +4345,21 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1275450307476970</t>
+          <t>1773179040333547</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4385,23 +4385,108 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>✨ Daily check-ins &amp; reminders</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>3778152075652558</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>✨ A friendly voice</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>17</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1456990959516034</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4418,7 +4503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -4435,7 +4520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-08 11:31 UTC</t>
+          <t>Generated: 2026-06-08 16:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4539,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -4464,7 +4549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7"/>
@@ -4499,14 +4584,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1265645248982771</t>
+          <t>1262827105689733</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1275450307476970</t>
+          <t>1265645248982771</t>
         </is>
       </c>
     </row>
@@ -4534,257 +4619,264 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1337913301639544</t>
+          <t>1333466355410690</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1389586346358002</t>
+          <t>1337913301639544</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1456990959516034</t>
+          <t>1389586346358002</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1473737363724928</t>
+          <t>1456990959516034</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1488992326012147</t>
+          <t>1473737363724928</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1496684578006716</t>
+          <t>1488992326012147</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1509948420588575</t>
+          <t>1496684578006716</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1533345218419188</t>
+          <t>1509948420588575</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1628987998235230</t>
+          <t>1533345218419188</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1631994437866750</t>
+          <t>1628987998235230</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1716989306388827</t>
+          <t>1631994437866750</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1718884162459661</t>
+          <t>1716989306388827</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1726022011744222</t>
+          <t>1718884162459661</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1748597059631955</t>
+          <t>1726022011744222</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1880751212615328</t>
+          <t>1748597059631955</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1902827973764397</t>
+          <t>1880751212615328</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2071219660470847</t>
+          <t>1888598388471432</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2157849958282307</t>
+          <t>1902827973764397</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2165050094062397</t>
+          <t>2071219660470847</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2265135094294745</t>
+          <t>2157849958282307</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>25522883924055159</t>
+          <t>2165050094062397</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>26907492185598691</t>
+          <t>2265135094294745</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3778152075652558</t>
+          <t>2438857833193853</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3911192652519370</t>
+          <t>25522883924055159</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4064887613808452</t>
+          <t>26907492185598691</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4562234493988358</t>
+          <t>3778152075652558</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4564425283883218</t>
+          <t>3911192652519370</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>824548033811820</t>
+          <t>4562234493988358</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>848561304926655</t>
+          <t>4564425283883218</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>877547294682816</t>
+          <t>824548033811820</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>884035753955138</t>
+          <t>848561304926655</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>890444574080612</t>
+          <t>877547294682816</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>969167216028774</t>
+          <t>884035753955138</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>970418362567584</t>
+          <t>890444574080612</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>973998952205878</t>
+          <t>969167216028774</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>974049545525369</t>
+          <t>973998952205878</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
+        <is>
+          <t>974049545525369</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>993138953210800</t>
         </is>
